--- a/team_leaders.xlsx
+++ b/team_leaders.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3308" uniqueCount="1074">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="1071">
   <si>
     <t xml:space="preserve">Team ID</t>
   </si>
@@ -3220,28 +3220,19 @@
     <t xml:space="preserve">2025-10-19T16:55:14.000Z</t>
   </si>
   <si>
-    <t xml:space="preserve">Manual1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LogicHigh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keerthan A K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">akkeerthan07@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manual2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tech Titan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guru ganesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guruganesh.23cs044@sode-edu.in</t>
+    <t xml:space="preserve">Manual3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeXphere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sahana M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sahanam9505@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maharaja Institute of Technology </t>
   </si>
 </sst>
 </file>
@@ -3540,7 +3531,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V195"/>
+  <dimension ref="A1:V1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="27.57"/>
@@ -3550,7 +3541,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="15.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="15.07"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15519,14 +15510,14 @@
         <v>38</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1" t="s">
+    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="0" t="s">
         <v>1066</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="C194" s="1" t="s">
+      <c r="C194" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D194" s="1" t="s">
@@ -15536,12 +15527,12 @@
         <v>1069</v>
       </c>
       <c r="F194" s="1" t="n">
-        <v>918050801998</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H194" s="1" t="s">
+        <v>918660136124</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H194" s="3" t="s">
         <v>222</v>
       </c>
       <c r="I194" s="1" t="s">
@@ -15553,64 +15544,19 @@
       <c r="K194" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="O194" s="1" t="n">
-        <v>2027</v>
-      </c>
       <c r="P194" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="T194" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="0" t="s">
         <v>1070</v>
       </c>
-      <c r="B195" s="1" t="s">
-        <v>1071</v>
-      </c>
-      <c r="C195" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F195" s="1" t="n">
-        <v>917975274584</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I195" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J195" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K195" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O195" s="0" t="n">
-        <v>2027</v>
-      </c>
-      <c r="P195" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="T195" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
+      <c r="T194" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V194" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E194" r:id="rId1" display="akkeerthan07@gmail.com"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/team_leaders.xlsx
+++ b/team_leaders.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3297" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="1087">
   <si>
     <t xml:space="preserve">Team ID</t>
   </si>
@@ -3233,6 +3233,54 @@
   </si>
   <si>
     <t xml:space="preserve">Maharaja Institute of Technology </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeCrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akshay Bhovi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">akshaynagaraj16112005@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">manual5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solution Squad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lavanya J S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lavanyalavanya9388@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LogicHigh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keerthan A K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">akkeerthan07@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manual2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tech Titan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guru ganesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guruganesh.23cs044@sode-edu.in</t>
   </si>
 </sst>
 </file>
@@ -3322,7 +3370,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3333,6 +3381,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -15511,7 +15563,7 @@
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A194" s="0" t="s">
+      <c r="A194" s="1" t="s">
         <v>1066</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -15551,12 +15603,170 @@
         <v>36</v>
       </c>
       <c r="V194" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="0" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B195" s="0" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C195" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F195" s="0" t="n">
+        <v>918660749860</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H195" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I195" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J195" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K195" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P195" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="T195" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V195" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="0" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B196" s="0" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C196" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D196" s="0" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E196" s="0" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F196" s="0" t="n">
+        <v>918088282948</v>
+      </c>
+      <c r="G196" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="H196" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="I196" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J196" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K196" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P196" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="T196" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V196" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="0" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F197" s="1" t="n">
+        <v>918050801998</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H197" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="P197" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="T197" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V197" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="0" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F198" s="1" t="n">
+        <v>917975274584</v>
+      </c>
+      <c r="H198" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="P198" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="T198" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="V198" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E195" r:id="rId1" display="akshaynagaraj16112005@gmail.com"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/team_leaders.xlsx
+++ b/team_leaders.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3291" uniqueCount="1069">
   <si>
     <t xml:space="preserve">Team ID</t>
   </si>
@@ -712,39 +712,21 @@
     <t xml:space="preserve">2025-10-09T12:07:16.000Z</t>
   </si>
   <si>
-    <t xml:space="preserve">U28K02VB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nitya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nityashree S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">nityashree.sg7@gmail.com</t>
+    <t xml:space="preserve">UBZ34N55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">codecatalyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINUSHA ACHARYA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vinusha.23ec098@sode-edu.in</t>
   </si>
   <si>
     <t xml:space="preserve">Electronics and Communication</t>
   </si>
   <si>
-    <t xml:space="preserve">BMS College of Engineering (BMSCE), Bangalore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-09T12:48:12.000Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBZ34N55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">codecatalyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VINUSHA ACHARYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vinusha.23ec098@sode-edu.in</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-10-09T14:28:07.000Z</t>
   </si>
   <si>
@@ -793,24 +775,6 @@
     <t xml:space="preserve">2025-10-09T18:04:17.000Z</t>
   </si>
   <si>
-    <t xml:space="preserve">UQTY1490</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kittu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanjay Rao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sanjayraops17@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mahatma Gandhi Memorial College Udupi, Udupi, Karnataka</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-10T05:31:29.000Z</t>
-  </si>
-  <si>
     <t xml:space="preserve">UV82T81A</t>
   </si>
   <si>
@@ -1145,24 +1109,6 @@
   </si>
   <si>
     <t xml:space="preserve">2025-10-13T01:29:17.000Z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U43IK83O</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Code smashers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suyash Patil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">suyashp812@gmail.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NITTE Institute of Professional Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-13T03:52:49.000Z</t>
   </si>
   <si>
     <t xml:space="preserve">U755BEJ1</t>
@@ -3370,7 +3316,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3384,10 +3330,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5860,13 +5802,13 @@
         <v>233</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>919481220954</v>
+        <v>918088265462</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>29</v>
@@ -5884,13 +5826,13 @@
         <v>4</v>
       </c>
       <c r="O37" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="P37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q37" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>236</v>
       </c>
       <c r="R37" s="1" t="s">
         <v>35</v>
@@ -5907,22 +5849,22 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="F38" s="1" t="n">
-        <v>918088265462</v>
+        <v>917618738827</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>148</v>
@@ -5940,19 +5882,19 @@
         <v>31</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>234</v>
+        <v>32</v>
       </c>
       <c r="N38" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O38" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>44</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R38" s="1" t="s">
         <v>35</v>
@@ -5969,22 +5911,22 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="F39" s="1" t="n">
-        <v>917618738827</v>
+        <v>919632858506</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>148</v>
@@ -6002,19 +5944,19 @@
         <v>31</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N39" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O39" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>35</v>
@@ -6031,25 +5973,25 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>250</v>
-      </c>
       <c r="F40" s="1" t="n">
-        <v>919632858506</v>
+        <v>917483242510</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H40" s="1" t="s">
         <v>28</v>
@@ -6070,13 +6012,13 @@
         <v>4</v>
       </c>
       <c r="O40" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R40" s="1" t="s">
         <v>35</v>
@@ -6093,25 +6035,25 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="C41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="F41" s="1" t="n">
-        <v>917483242510</v>
+        <v>919420529464</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H41" s="1" t="s">
         <v>28</v>
@@ -6126,7 +6068,7 @@
         <v>31</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="N41" s="1" t="n">
         <v>4</v>
@@ -6135,10 +6077,10 @@
         <v>2028</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="R41" s="1" t="s">
         <v>35</v>
@@ -6155,25 +6097,25 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="C42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C42" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="F42" s="1" t="n">
-        <v>917483050218</v>
+        <v>918310005700</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>28</v>
@@ -6188,19 +6130,19 @@
         <v>31</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>32</v>
+        <v>234</v>
       </c>
       <c r="N42" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O42" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>261</v>
+        <v>44</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="R42" s="1" t="s">
         <v>35</v>
@@ -6217,22 +6159,22 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>266</v>
-      </c>
       <c r="F43" s="1" t="n">
-        <v>919420529464</v>
+        <v>916361126213</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>148</v>
@@ -6250,19 +6192,19 @@
         <v>31</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="N43" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O43" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P43" s="1" t="s">
         <v>63</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R43" s="1" t="s">
         <v>35</v>
@@ -6279,28 +6221,28 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="F44" s="1" t="n">
-        <v>918310005700</v>
+        <v>918296990207</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>29</v>
@@ -6312,7 +6254,7 @@
         <v>31</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>234</v>
+        <v>51</v>
       </c>
       <c r="N44" s="1" t="n">
         <v>4</v>
@@ -6321,10 +6263,10 @@
         <v>2027</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>44</v>
+        <v>270</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>35</v>
@@ -6341,22 +6283,22 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>276</v>
-      </c>
       <c r="F45" s="1" t="n">
-        <v>916361126213</v>
+        <v>918050091054</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>148</v>
@@ -6374,19 +6316,19 @@
         <v>31</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>51</v>
+        <v>234</v>
       </c>
       <c r="N45" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O45" s="1" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>35</v>
@@ -6403,28 +6345,28 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="C46" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="F46" s="1" t="n">
-        <v>918296990207</v>
+        <v>918867060029</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>29</v>
@@ -6442,13 +6384,13 @@
         <v>4</v>
       </c>
       <c r="O46" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>282</v>
+        <v>44</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="R46" s="1" t="s">
         <v>35</v>
@@ -6465,52 +6407,52 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C47" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="1" t="s">
+      <c r="F47" s="1" t="n">
+        <v>918050390858</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O47" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P47" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="Q47" s="1" t="s">
         <v>287</v>
-      </c>
-      <c r="F47" s="1" t="n">
-        <v>918050091054</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="N47" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O47" s="1" t="n">
-        <v>2029</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>288</v>
       </c>
       <c r="R47" s="1" t="s">
         <v>35</v>
@@ -6527,25 +6469,25 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="C48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="F48" s="1" t="n">
-        <v>918867060029</v>
+        <v>916360850145</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H48" s="1" t="s">
         <v>28</v>
@@ -6560,16 +6502,16 @@
         <v>31</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>51</v>
+        <v>292</v>
       </c>
       <c r="N48" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O48" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="Q48" s="1" t="s">
         <v>293</v>
@@ -6604,13 +6546,13 @@
         <v>297</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>918050390858</v>
+        <v>919168214473</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>29</v>
@@ -6622,19 +6564,19 @@
         <v>31</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N49" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O49" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P49" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q49" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="R49" s="1" t="s">
         <v>35</v>
@@ -6651,22 +6593,22 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="F50" s="1" t="n">
-        <v>916360850145</v>
+        <v>917204643772</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>27</v>
@@ -6684,19 +6626,19 @@
         <v>31</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>304</v>
+        <v>51</v>
       </c>
       <c r="N50" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O50" s="1" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>196</v>
+        <v>63</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>35</v>
@@ -6713,28 +6655,28 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="E51" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>309</v>
-      </c>
       <c r="F51" s="1" t="n">
-        <v>919168214473</v>
+        <v>919633237124</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>29</v>
@@ -6746,19 +6688,19 @@
         <v>31</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>32</v>
+        <v>308</v>
       </c>
       <c r="N51" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O51" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="R51" s="1" t="s">
         <v>35</v>
@@ -6775,25 +6717,25 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="C52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="F52" s="1" t="n">
-        <v>917204643772</v>
+        <v>916366119677</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>28</v>
@@ -6814,13 +6756,13 @@
         <v>4</v>
       </c>
       <c r="O52" s="1" t="n">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>63</v>
+        <v>190</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="R52" s="1" t="s">
         <v>35</v>
@@ -6837,28 +6779,28 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="C53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>319</v>
-      </c>
       <c r="F53" s="1" t="n">
-        <v>919633237124</v>
+        <v>919008667579</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>29</v>
@@ -6870,19 +6812,19 @@
         <v>31</v>
       </c>
       <c r="L53" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="N53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O53" s="1" t="n">
+        <v>2028</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q53" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="N53" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O53" s="1" t="n">
-        <v>2027</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>321</v>
       </c>
       <c r="R53" s="1" t="s">
         <v>35</v>
@@ -6899,49 +6841,49 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="C54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="F54" s="1" t="n">
+        <v>919035973058</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N54" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O54" s="1" t="n">
+        <v>2028</v>
+      </c>
+      <c r="P54" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="F54" s="1" t="n">
-        <v>916366119677</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J54" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N54" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O54" s="1" t="n">
-        <v>2027</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>190</v>
       </c>
       <c r="Q54" s="1" t="s">
         <v>326</v>
@@ -6976,7 +6918,7 @@
         <v>330</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>919008667579</v>
+        <v>917349341496</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>148</v>
@@ -6994,19 +6936,19 @@
         <v>31</v>
       </c>
       <c r="L55" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O55" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q55" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="N55" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O55" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="P55" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="R55" s="1" t="s">
         <v>35</v>
@@ -7023,52 +6965,52 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="C56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="F56" s="1" t="n">
+        <v>919380729364</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O56" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q56" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="F56" s="1" t="n">
-        <v>919035973058</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N56" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O56" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="R56" s="1" t="s">
         <v>35</v>
@@ -7085,22 +7027,22 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="E57" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>342</v>
-      </c>
       <c r="F57" s="1" t="n">
-        <v>917349341496</v>
+        <v>918904311968</v>
       </c>
       <c r="G57" s="1" t="s">
         <v>148</v>
@@ -7118,19 +7060,19 @@
         <v>31</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>51</v>
+        <v>135</v>
       </c>
       <c r="N57" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O57" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="R57" s="1" t="s">
         <v>35</v>
@@ -7147,22 +7089,22 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="F58" s="1" t="n">
-        <v>919380729364</v>
+        <v>918904652494</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>148</v>
@@ -7186,13 +7128,13 @@
         <v>4</v>
       </c>
       <c r="O58" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="R58" s="1" t="s">
         <v>35</v>
@@ -7209,28 +7151,28 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="E59" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="F59" s="1" t="n">
-        <v>918904311968</v>
+        <v>919110457001</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>29</v>
@@ -7242,19 +7184,19 @@
         <v>31</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="N59" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O59" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>35</v>
@@ -7271,25 +7213,25 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="E60" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>357</v>
-      </c>
       <c r="F60" s="1" t="n">
-        <v>918904652494</v>
+        <v>919060159605</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H60" s="1" t="s">
         <v>28</v>
@@ -7304,19 +7246,19 @@
         <v>31</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N60" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O60" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>44</v>
+        <v>356</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R60" s="1" t="s">
         <v>35</v>
@@ -7333,52 +7275,52 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="F61" s="1" t="n">
+        <v>919731064970</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O61" s="1" t="n">
+        <v>2028</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q61" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="F61" s="1" t="n">
-        <v>919110457001</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N61" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O61" s="1" t="n">
-        <v>2027</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="R61" s="1" t="s">
         <v>35</v>
@@ -7395,22 +7337,22 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="C62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="F62" s="1" t="n">
-        <v>919060159605</v>
+        <v>918073109441</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>27</v>
@@ -7428,19 +7370,19 @@
         <v>31</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N62" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O62" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>368</v>
+        <v>44</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>35</v>
@@ -7457,28 +7399,28 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="F63" s="1" t="n">
-        <v>919731064970</v>
+        <v>919880958141</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>29</v>
@@ -7490,19 +7432,19 @@
         <v>31</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N63" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O63" s="1" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="R63" s="1" t="s">
         <v>35</v>
@@ -7519,28 +7461,28 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C64" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="F64" s="1" t="n">
-        <v>917219822622</v>
+        <v>918310274475</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>29</v>
@@ -7552,19 +7494,19 @@
         <v>31</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>32</v>
+        <v>234</v>
       </c>
       <c r="N64" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O64" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>35</v>
@@ -7581,25 +7523,25 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="E65" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="F65" s="1" t="n">
-        <v>918073109441</v>
+        <v>919632545120</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>28</v>
@@ -7626,7 +7568,7 @@
         <v>44</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="R65" s="1" t="s">
         <v>35</v>
@@ -7643,28 +7585,28 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="E66" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>389</v>
-      </c>
       <c r="F66" s="1" t="n">
-        <v>919880958141</v>
+        <v>918310764938</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>29</v>
@@ -7682,13 +7624,13 @@
         <v>4</v>
       </c>
       <c r="O66" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>52</v>
+        <v>388</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R66" s="1" t="s">
         <v>35</v>
@@ -7705,28 +7647,28 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="C67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C67" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>394</v>
-      </c>
       <c r="F67" s="1" t="n">
-        <v>918310274475</v>
+        <v>919743067675</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>29</v>
@@ -7738,19 +7680,19 @@
         <v>31</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>234</v>
+        <v>51</v>
       </c>
       <c r="N67" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O67" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P67" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="Q67" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>396</v>
       </c>
       <c r="R67" s="1" t="s">
         <v>35</v>
@@ -7767,25 +7709,25 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="C68" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="F68" s="1" t="n">
-        <v>919632545120</v>
+        <v>916364184680</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>28</v>
@@ -7800,19 +7742,19 @@
         <v>31</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>51</v>
+        <v>292</v>
       </c>
       <c r="N68" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O68" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>44</v>
+        <v>196</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="R68" s="1" t="s">
         <v>35</v>
@@ -7829,28 +7771,28 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="C69" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="F69" s="1" t="n">
-        <v>918310764938</v>
+        <v>919663556801</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>29</v>
@@ -7868,22 +7810,19 @@
         <v>4</v>
       </c>
       <c r="O69" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P69" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q69" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="Q69" s="1" t="s">
-        <v>407</v>
-      </c>
       <c r="R69" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T69" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V69" s="1" t="s">
         <v>38</v>
@@ -7891,61 +7830,58 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="F70" s="1" t="n">
+        <v>916366258564</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N70" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O70" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q70" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="F70" s="1" t="n">
-        <v>919743067675</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N70" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O70" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>413</v>
-      </c>
       <c r="R70" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T70" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U70" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V70" s="1" t="s">
         <v>38</v>
@@ -7953,22 +7889,22 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="E71" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>417</v>
-      </c>
       <c r="F71" s="1" t="n">
-        <v>916364184680</v>
+        <v>918867494183</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>27</v>
@@ -7986,19 +7922,19 @@
         <v>31</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>304</v>
+        <v>32</v>
       </c>
       <c r="N71" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O71" s="1" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>35</v>
@@ -8015,25 +7951,25 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="E72" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="C72" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>422</v>
-      </c>
       <c r="F72" s="1" t="n">
-        <v>919663556801</v>
+        <v>918088651553</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>69</v>
@@ -8054,19 +7990,22 @@
         <v>4</v>
       </c>
       <c r="O72" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>423</v>
+        <v>190</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="R72" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T72" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V72" s="1" t="s">
         <v>38</v>
@@ -8074,29 +8013,29 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="F73" s="1" t="n">
+        <v>918088895389</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H73" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C73" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="F73" s="1" t="n">
-        <v>916366258564</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H73" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="I73" s="1" t="s">
         <v>29</v>
       </c>
@@ -8107,7 +8046,10 @@
         <v>31</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>234</v>
+        <v>51</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="N73" s="1" t="n">
         <v>4</v>
@@ -8116,16 +8058,19 @@
         <v>2027</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>44</v>
+        <v>427</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T73" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V73" s="1" t="s">
         <v>38</v>
@@ -8133,25 +8078,25 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="C74" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>433</v>
-      </c>
       <c r="F74" s="1" t="n">
-        <v>918867494183</v>
+        <v>919449096747</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>28</v>
@@ -8166,19 +8111,19 @@
         <v>31</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N74" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O74" s="1" t="n">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="P74" s="1" t="s">
-        <v>44</v>
+        <v>356</v>
       </c>
       <c r="Q74" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="R74" s="1" t="s">
         <v>35</v>
@@ -8195,28 +8140,28 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>438</v>
-      </c>
       <c r="F75" s="1" t="n">
-        <v>918088651553</v>
+        <v>918431988184</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>29</v>
@@ -8237,10 +8182,10 @@
         <v>2027</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>190</v>
+        <v>356</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="R75" s="1" t="s">
         <v>35</v>
@@ -8257,28 +8202,28 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>443</v>
-      </c>
       <c r="F76" s="1" t="n">
-        <v>918088895389</v>
+        <v>919741358693</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>444</v>
+        <v>28</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>29</v>
@@ -8292,20 +8237,17 @@
       <c r="L76" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M76" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="N76" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O76" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>445</v>
+        <v>44</v>
       </c>
       <c r="Q76" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>35</v>
@@ -8322,22 +8264,22 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>450</v>
-      </c>
       <c r="F77" s="1" t="n">
-        <v>919449096747</v>
+        <v>917975107669</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>148</v>
@@ -8355,19 +8297,19 @@
         <v>31</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N77" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O77" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>368</v>
+        <v>63</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="R77" s="1" t="s">
         <v>35</v>
@@ -8384,28 +8326,28 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>455</v>
-      </c>
       <c r="F78" s="1" t="n">
-        <v>918431988184</v>
+        <v>919480119879</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>29</v>
@@ -8426,19 +8368,16 @@
         <v>2027</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>368</v>
+        <v>190</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T78" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U78" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V78" s="1" t="s">
         <v>38</v>
@@ -8446,22 +8385,22 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>460</v>
-      </c>
       <c r="F79" s="1" t="n">
-        <v>919741358693</v>
+        <v>918073217492</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>148</v>
@@ -8488,10 +8427,10 @@
         <v>2028</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="Q79" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="R79" s="1" t="s">
         <v>35</v>
@@ -8508,22 +8447,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="E80" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="F80" s="1" t="n">
-        <v>917975107669</v>
+        <v>918762149928</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>148</v>
@@ -8541,19 +8480,19 @@
         <v>31</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N80" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O80" s="1" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="P80" s="1" t="s">
         <v>63</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="R80" s="1" t="s">
         <v>35</v>
@@ -8570,22 +8509,22 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>468</v>
+        <v>278</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>919480119879</v>
+        <v>916361438625</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>27</v>
@@ -8603,25 +8542,28 @@
         <v>31</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N81" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O81" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>190</v>
+        <v>467</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T81" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U81" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V81" s="1" t="s">
         <v>38</v>
@@ -8629,22 +8571,22 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="E82" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>475</v>
-      </c>
       <c r="F82" s="1" t="n">
-        <v>918073217492</v>
+        <v>918088334739</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>148</v>
@@ -8662,19 +8604,19 @@
         <v>31</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>51</v>
+        <v>473</v>
       </c>
       <c r="N82" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O82" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>63</v>
+        <v>474</v>
       </c>
       <c r="Q82" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>35</v>
@@ -8691,22 +8633,22 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>480</v>
-      </c>
       <c r="F83" s="1" t="n">
-        <v>918762149928</v>
+        <v>919113813480</v>
       </c>
       <c r="G83" s="1" t="s">
         <v>148</v>
@@ -8730,10 +8672,10 @@
         <v>4</v>
       </c>
       <c r="O83" s="1" t="n">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>63</v>
+        <v>480</v>
       </c>
       <c r="Q83" s="1" t="s">
         <v>481</v>
@@ -8756,25 +8698,25 @@
         <v>482</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>290</v>
+        <v>483</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>916361438625</v>
+        <v>916362391028</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H84" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>29</v>
@@ -8792,22 +8734,19 @@
         <v>4</v>
       </c>
       <c r="O84" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q84" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="R84" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T84" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U84" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V84" s="1" t="s">
         <v>38</v>
@@ -8815,28 +8754,28 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>918088334739</v>
+        <v>918105700380</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>28</v>
+        <v>492</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>29</v>
@@ -8848,19 +8787,22 @@
         <v>31</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>491</v>
+        <v>51</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="N85" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O85" s="1" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>35</v>
@@ -8877,22 +8819,22 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>919113813480</v>
+        <v>919663729636</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>148</v>
@@ -8919,10 +8861,10 @@
         <v>2027</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="R86" s="1" t="s">
         <v>35</v>
@@ -8939,28 +8881,28 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>916362391028</v>
+        <v>918317462979</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H87" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>29</v>
@@ -8981,7 +8923,7 @@
         <v>2027</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>504</v>
+        <v>394</v>
       </c>
       <c r="Q87" s="1" t="s">
         <v>505</v>
@@ -8991,6 +8933,9 @@
       </c>
       <c r="T87" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U87" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V87" s="1" t="s">
         <v>38</v>
@@ -9013,13 +8958,13 @@
         <v>509</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>918105700380</v>
+        <v>918970599215</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H88" s="1" t="s">
-        <v>510</v>
+        <v>28</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>29</v>
@@ -9033,20 +8978,17 @@
       <c r="L88" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="M88" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="N88" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O88" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>511</v>
+        <v>190</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="R88" s="1" t="s">
         <v>35</v>
@@ -9063,28 +9005,28 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="F89" s="1" t="n">
-        <v>919663729636</v>
+        <v>917795912966</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>29</v>
@@ -9105,10 +9047,10 @@
         <v>2027</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>517</v>
+        <v>356</v>
       </c>
       <c r="Q89" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="R89" s="1" t="s">
         <v>35</v>
@@ -9125,28 +9067,28 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>521</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="F90" s="1" t="n">
-        <v>918317462979</v>
+        <v>916362414596</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>29</v>
@@ -9158,7 +9100,7 @@
         <v>31</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N90" s="1" t="n">
         <v>4</v>
@@ -9167,10 +9109,10 @@
         <v>2027</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>412</v>
+        <v>190</v>
       </c>
       <c r="Q90" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>35</v>
@@ -9187,28 +9129,28 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>527</v>
-      </c>
       <c r="F91" s="1" t="n">
-        <v>918970599215</v>
+        <v>917019267494</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H91" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>29</v>
@@ -9220,7 +9162,7 @@
         <v>31</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>51</v>
+        <v>319</v>
       </c>
       <c r="N91" s="1" t="n">
         <v>4</v>
@@ -9229,10 +9171,10 @@
         <v>2027</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>190</v>
+        <v>394</v>
       </c>
       <c r="Q91" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="R91" s="1" t="s">
         <v>35</v>
@@ -9249,28 +9191,28 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="E92" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>532</v>
-      </c>
       <c r="F92" s="1" t="n">
-        <v>917795912966</v>
+        <v>918310938562</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H92" s="1" t="s">
-        <v>69</v>
+        <v>222</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>29</v>
@@ -9291,10 +9233,10 @@
         <v>2027</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>368</v>
+        <v>499</v>
       </c>
       <c r="Q92" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="R92" s="1" t="s">
         <v>35</v>
@@ -9311,25 +9253,25 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="E93" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="F93" s="1" t="n">
-        <v>916362414596</v>
+        <v>919481878989</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H93" s="1" t="s">
         <v>28</v>
@@ -9356,7 +9298,7 @@
         <v>190</v>
       </c>
       <c r="Q93" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>35</v>
@@ -9373,28 +9315,28 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>540</v>
+        <v>402</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>917019267494</v>
+        <v>917975402353</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>29</v>
@@ -9406,19 +9348,19 @@
         <v>31</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>331</v>
+        <v>51</v>
       </c>
       <c r="N94" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O94" s="1" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>412</v>
+        <v>493</v>
       </c>
       <c r="Q94" s="1" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="R94" s="1" t="s">
         <v>35</v>
@@ -9435,28 +9377,28 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>918310938562</v>
+        <v>917760989192</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H95" s="1" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>29</v>
@@ -9468,19 +9410,19 @@
         <v>31</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>51</v>
+        <v>234</v>
       </c>
       <c r="N95" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O95" s="1" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>517</v>
+        <v>44</v>
       </c>
       <c r="Q95" s="1" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="R95" s="1" t="s">
         <v>35</v>
@@ -9497,52 +9439,52 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>917892898560</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I96" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N96" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O96" s="1" t="n">
+        <v>2029</v>
+      </c>
+      <c r="P96" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q96" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="F96" s="1" t="n">
-        <v>919481878989</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I96" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J96" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N96" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O96" s="1" t="n">
-        <v>2027</v>
-      </c>
-      <c r="P96" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q96" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="R96" s="1" t="s">
         <v>35</v>
@@ -9559,52 +9501,52 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>919148669628</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L97" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D97" s="1" t="s">
+      <c r="N97" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O97" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P97" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q97" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="F97" s="1" t="n">
-        <v>917975402353</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H97" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I97" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J97" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N97" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O97" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="P97" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="Q97" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="R97" s="1" t="s">
         <v>35</v>
@@ -9621,28 +9563,28 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="F98" s="1" t="n">
-        <v>917760989192</v>
+        <v>918217612080</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>29</v>
@@ -9654,19 +9596,19 @@
         <v>31</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>234</v>
+        <v>32</v>
       </c>
       <c r="N98" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O98" s="1" t="n">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="Q98" s="1" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="R98" s="1" t="s">
         <v>35</v>
@@ -9683,52 +9625,52 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D99" s="1" t="s">
+      <c r="F99" s="1" t="n">
+        <v>919035703138</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N99" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O99" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q99" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="F99" s="1" t="n">
-        <v>917892898560</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H99" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="I99" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J99" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N99" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O99" s="1" t="n">
-        <v>2029</v>
-      </c>
-      <c r="P99" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q99" s="1" t="s">
-        <v>567</v>
       </c>
       <c r="R99" s="1" t="s">
         <v>35</v>
@@ -9745,25 +9687,25 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="C100" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>571</v>
-      </c>
       <c r="F100" s="1" t="n">
-        <v>919148669628</v>
+        <v>916360457007</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H100" s="1" t="s">
         <v>28</v>
@@ -9778,7 +9720,7 @@
         <v>31</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>572</v>
+        <v>51</v>
       </c>
       <c r="N100" s="1" t="n">
         <v>4</v>
@@ -9790,7 +9732,7 @@
         <v>190</v>
       </c>
       <c r="Q100" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>35</v>
@@ -9807,28 +9749,28 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>574</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>577</v>
-      </c>
       <c r="F101" s="1" t="n">
-        <v>918217612080</v>
+        <v>917021026606</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>29</v>
@@ -9849,10 +9791,10 @@
         <v>2027</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>190</v>
+        <v>575</v>
       </c>
       <c r="Q101" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>35</v>
@@ -9869,28 +9811,28 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>582</v>
-      </c>
       <c r="F102" s="1" t="n">
-        <v>919035703138</v>
+        <v>917760822949</v>
       </c>
       <c r="G102" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>29</v>
@@ -9914,7 +9856,7 @@
         <v>190</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>35</v>
@@ -9931,28 +9873,28 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>583</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>587</v>
-      </c>
       <c r="F103" s="1" t="n">
-        <v>916360457007</v>
+        <v>919620192583</v>
       </c>
       <c r="G103" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H103" s="1" t="s">
-        <v>28</v>
+        <v>586</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>29</v>
@@ -9973,7 +9915,7 @@
         <v>2027</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>190</v>
+        <v>587</v>
       </c>
       <c r="Q103" s="1" t="s">
         <v>588</v>
@@ -10008,10 +9950,10 @@
         <v>592</v>
       </c>
       <c r="F104" s="1" t="n">
-        <v>917021026606</v>
+        <v>919945437337</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>28</v>
@@ -10026,19 +9968,19 @@
         <v>31</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>32</v>
+        <v>234</v>
       </c>
       <c r="N104" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O104" s="1" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="P104" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q104" s="1" t="s">
         <v>593</v>
-      </c>
-      <c r="Q104" s="1" t="s">
-        <v>594</v>
       </c>
       <c r="R104" s="1" t="s">
         <v>35</v>
@@ -10055,28 +9997,28 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="C105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="C105" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D105" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="E105" s="1" t="s">
-        <v>598</v>
-      </c>
       <c r="F105" s="1" t="n">
-        <v>917760822949</v>
+        <v>919606158823</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>29</v>
@@ -10088,7 +10030,7 @@
         <v>31</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N105" s="1" t="n">
         <v>4</v>
@@ -10100,7 +10042,7 @@
         <v>190</v>
       </c>
       <c r="Q105" s="1" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="R105" s="1" t="s">
         <v>35</v>
@@ -10117,28 +10059,28 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C106" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>603</v>
-      </c>
       <c r="F106" s="1" t="n">
-        <v>919620192583</v>
+        <v>918762509780</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H106" s="1" t="s">
-        <v>604</v>
+        <v>134</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>29</v>
@@ -10156,13 +10098,13 @@
         <v>4</v>
       </c>
       <c r="O106" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P106" s="1" t="s">
-        <v>605</v>
+        <v>44</v>
       </c>
       <c r="Q106" s="1" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="R106" s="1" t="s">
         <v>35</v>
@@ -10179,28 +10121,28 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="F107" s="1" t="n">
-        <v>919945437337</v>
+        <v>917760802159</v>
       </c>
       <c r="G107" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>28</v>
+        <v>222</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>29</v>
@@ -10212,19 +10154,22 @@
         <v>31</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>234</v>
+        <v>51</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="N107" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O107" s="1" t="n">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>44</v>
+        <v>499</v>
       </c>
       <c r="Q107" s="1" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>35</v>
@@ -10241,22 +10186,22 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="F108" s="1" t="n">
-        <v>919606158823</v>
+        <v>919148181857</v>
       </c>
       <c r="G108" s="1" t="s">
         <v>148</v>
@@ -10274,7 +10219,7 @@
         <v>31</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N108" s="1" t="n">
         <v>4</v>
@@ -10283,10 +10228,10 @@
         <v>2027</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>190</v>
+        <v>493</v>
       </c>
       <c r="Q108" s="1" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="R108" s="1" t="s">
         <v>35</v>
@@ -10303,28 +10248,28 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="F109" s="1" t="n">
-        <v>918762509780</v>
+        <v>918660843693</v>
       </c>
       <c r="G109" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>29</v>
@@ -10342,13 +10287,13 @@
         <v>4</v>
       </c>
       <c r="O109" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>35</v>
@@ -10365,28 +10310,28 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="E110" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="F110" s="1" t="n">
-        <v>917760802159</v>
+        <v>918792127382</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H110" s="1" t="s">
-        <v>222</v>
+        <v>69</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>29</v>
@@ -10398,10 +10343,7 @@
         <v>31</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M110" s="1" t="s">
-        <v>102</v>
+        <v>308</v>
       </c>
       <c r="N110" s="1" t="n">
         <v>4</v>
@@ -10410,10 +10352,10 @@
         <v>2027</v>
       </c>
       <c r="P110" s="1" t="s">
-        <v>517</v>
+        <v>190</v>
       </c>
       <c r="Q110" s="1" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="R110" s="1" t="s">
         <v>35</v>
@@ -10430,28 +10372,28 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>628</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="F111" s="1" t="n">
-        <v>919148181857</v>
+        <v>919900450852</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>29</v>
@@ -10472,10 +10414,10 @@
         <v>2027</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>511</v>
+        <v>627</v>
       </c>
       <c r="Q111" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>35</v>
@@ -10492,28 +10434,28 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="E112" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>634</v>
-      </c>
       <c r="F112" s="1" t="n">
-        <v>918660843693</v>
+        <v>919480763829</v>
       </c>
       <c r="G112" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H112" s="1" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>29</v>
@@ -10525,7 +10467,7 @@
         <v>31</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>51</v>
+        <v>308</v>
       </c>
       <c r="N112" s="1" t="n">
         <v>4</v>
@@ -10534,10 +10476,10 @@
         <v>2027</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>190</v>
+        <v>467</v>
       </c>
       <c r="Q112" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="R112" s="1" t="s">
         <v>35</v>
@@ -10554,28 +10496,28 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="E113" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>639</v>
-      </c>
       <c r="F113" s="1" t="n">
-        <v>918792127382</v>
+        <v>918792646521</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H113" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>29</v>
@@ -10587,19 +10529,19 @@
         <v>31</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>320</v>
+        <v>43</v>
       </c>
       <c r="N113" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O113" s="1" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P113" s="1" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="Q113" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="R113" s="1" t="s">
         <v>35</v>
@@ -10616,28 +10558,28 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="E114" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>643</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="F114" s="1" t="n">
-        <v>919900450852</v>
+        <v>919113094089</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>134</v>
+        <v>643</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>29</v>
@@ -10658,10 +10600,10 @@
         <v>2027</v>
       </c>
       <c r="P114" s="1" t="s">
-        <v>645</v>
+        <v>190</v>
       </c>
       <c r="Q114" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="R114" s="1" t="s">
         <v>35</v>
@@ -10678,28 +10620,28 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="E115" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>650</v>
-      </c>
       <c r="F115" s="1" t="n">
-        <v>919480763829</v>
+        <v>919110819297</v>
       </c>
       <c r="G115" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H115" s="1" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>29</v>
@@ -10711,7 +10653,7 @@
         <v>31</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>320</v>
+        <v>32</v>
       </c>
       <c r="N115" s="1" t="n">
         <v>4</v>
@@ -10720,10 +10662,10 @@
         <v>2027</v>
       </c>
       <c r="P115" s="1" t="s">
-        <v>485</v>
+        <v>649</v>
       </c>
       <c r="Q115" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>35</v>
@@ -10740,28 +10682,28 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>655</v>
-      </c>
       <c r="F116" s="1" t="n">
-        <v>918792646521</v>
+        <v>919113851473</v>
       </c>
       <c r="G116" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H116" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>29</v>
@@ -10773,16 +10715,19 @@
         <v>31</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>43</v>
+        <v>319</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="N116" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O116" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="P116" s="1" t="s">
-        <v>44</v>
+        <v>655</v>
       </c>
       <c r="Q116" s="1" t="s">
         <v>656</v>
@@ -10817,13 +10762,13 @@
         <v>660</v>
       </c>
       <c r="F117" s="1" t="n">
-        <v>919113094089</v>
+        <v>918296338351</v>
       </c>
       <c r="G117" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>661</v>
+        <v>28</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>29</v>
@@ -10844,10 +10789,10 @@
         <v>2027</v>
       </c>
       <c r="P117" s="1" t="s">
-        <v>190</v>
+        <v>499</v>
       </c>
       <c r="Q117" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="R117" s="1" t="s">
         <v>35</v>
@@ -10864,28 +10809,28 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="C118" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>666</v>
-      </c>
       <c r="F118" s="1" t="n">
-        <v>919110819297</v>
+        <v>917975084716</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>29</v>
@@ -10897,7 +10842,7 @@
         <v>31</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N118" s="1" t="n">
         <v>4</v>
@@ -10906,10 +10851,10 @@
         <v>2027</v>
       </c>
       <c r="P118" s="1" t="s">
-        <v>667</v>
+        <v>190</v>
       </c>
       <c r="Q118" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="R118" s="1" t="s">
         <v>35</v>
@@ -10926,28 +10871,28 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="E119" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>672</v>
-      </c>
       <c r="F119" s="1" t="n">
-        <v>919113851473</v>
+        <v>918660226050</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>50</v>
+        <v>426</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>29</v>
@@ -10959,10 +10904,7 @@
         <v>31</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="M119" s="1" t="s">
-        <v>102</v>
+        <v>32</v>
       </c>
       <c r="N119" s="1" t="n">
         <v>4</v>
@@ -10971,10 +10913,10 @@
         <v>2027</v>
       </c>
       <c r="P119" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="Q119" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="R119" s="1" t="s">
         <v>35</v>
@@ -10991,25 +10933,25 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="E120" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>678</v>
-      </c>
       <c r="F120" s="1" t="n">
-        <v>918296338351</v>
+        <v>918762380667</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>28</v>
@@ -11033,19 +10975,16 @@
         <v>2027</v>
       </c>
       <c r="P120" s="1" t="s">
-        <v>517</v>
+        <v>190</v>
       </c>
       <c r="Q120" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="R120" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T120" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U120" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V120" s="1" t="s">
         <v>38</v>
@@ -11053,28 +10992,28 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="E121" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>683</v>
-      </c>
       <c r="F121" s="1" t="n">
-        <v>917975084716</v>
+        <v>917204191965</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H121" s="1" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>29</v>
@@ -11095,10 +11034,10 @@
         <v>2027</v>
       </c>
       <c r="P121" s="1" t="s">
-        <v>190</v>
+        <v>427</v>
       </c>
       <c r="Q121" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="R121" s="1" t="s">
         <v>35</v>
@@ -11115,28 +11054,28 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="E122" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>687</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="F122" s="1" t="n">
-        <v>918660226050</v>
+        <v>918951812059</v>
       </c>
       <c r="G122" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>444</v>
+        <v>28</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>29</v>
@@ -11148,7 +11087,7 @@
         <v>31</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N122" s="1" t="n">
         <v>4</v>
@@ -11157,10 +11096,10 @@
         <v>2027</v>
       </c>
       <c r="P122" s="1" t="s">
-        <v>689</v>
+        <v>499</v>
       </c>
       <c r="Q122" s="1" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="R122" s="1" t="s">
         <v>35</v>
@@ -11177,28 +11116,28 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="E123" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B123" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>694</v>
-      </c>
       <c r="F123" s="1" t="n">
-        <v>918762380667</v>
+        <v>918792451559</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>29</v>
@@ -11210,7 +11149,7 @@
         <v>31</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N123" s="1" t="n">
         <v>4</v>
@@ -11219,16 +11158,19 @@
         <v>2027</v>
       </c>
       <c r="P123" s="1" t="s">
-        <v>190</v>
+        <v>692</v>
       </c>
       <c r="Q123" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="R123" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T123" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U123" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V123" s="1" t="s">
         <v>38</v>
@@ -11236,28 +11178,28 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="E124" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="F124" s="1" t="n">
-        <v>917204191965</v>
+        <v>916362442368</v>
       </c>
       <c r="G124" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H124" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>29</v>
@@ -11275,13 +11217,13 @@
         <v>4</v>
       </c>
       <c r="O124" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P124" s="1" t="s">
-        <v>445</v>
+        <v>33</v>
       </c>
       <c r="Q124" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="R124" s="1" t="s">
         <v>35</v>
@@ -11298,28 +11240,28 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>703</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>704</v>
-      </c>
       <c r="F125" s="1" t="n">
-        <v>918951812059</v>
+        <v>919945043670</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H125" s="1" t="s">
-        <v>28</v>
+        <v>703</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>29</v>
@@ -11331,16 +11273,16 @@
         <v>31</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N125" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O125" s="1" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P125" s="1" t="s">
-        <v>517</v>
+        <v>704</v>
       </c>
       <c r="Q125" s="1" t="s">
         <v>705</v>
@@ -11375,13 +11317,13 @@
         <v>709</v>
       </c>
       <c r="F126" s="1" t="n">
-        <v>918792451559</v>
+        <v>918197887939</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H126" s="1" t="s">
-        <v>134</v>
+        <v>586</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>29</v>
@@ -11393,7 +11335,7 @@
         <v>31</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="N126" s="1" t="n">
         <v>4</v>
@@ -11437,13 +11379,13 @@
         <v>715</v>
       </c>
       <c r="F127" s="1" t="n">
-        <v>916362442368</v>
+        <v>918867454402</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H127" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>29</v>
@@ -11461,10 +11403,10 @@
         <v>4</v>
       </c>
       <c r="O127" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>33</v>
+        <v>499</v>
       </c>
       <c r="Q127" s="1" t="s">
         <v>716</v>
@@ -11499,7 +11441,7 @@
         <v>720</v>
       </c>
       <c r="F128" s="1" t="n">
-        <v>919945043670</v>
+        <v>917204765099</v>
       </c>
       <c r="G128" s="1" t="s">
         <v>27</v>
@@ -11517,13 +11459,13 @@
         <v>31</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="N128" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O128" s="1" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="P128" s="1" t="s">
         <v>722</v>
@@ -11561,13 +11503,13 @@
         <v>727</v>
       </c>
       <c r="F129" s="1" t="n">
-        <v>918197887939</v>
+        <v>919353250245</v>
       </c>
       <c r="G129" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>604</v>
+        <v>28</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>29</v>
@@ -11623,13 +11565,13 @@
         <v>733</v>
       </c>
       <c r="F130" s="1" t="n">
-        <v>918867454402</v>
+        <v>919611842780</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>28</v>
+        <v>643</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>29</v>
@@ -11647,10 +11589,10 @@
         <v>4</v>
       </c>
       <c r="O130" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P130" s="1" t="s">
-        <v>517</v>
+        <v>190</v>
       </c>
       <c r="Q130" s="1" t="s">
         <v>734</v>
@@ -11685,46 +11627,43 @@
         <v>738</v>
       </c>
       <c r="F131" s="1" t="n">
-        <v>917204765099</v>
+        <v>919686074527</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H131" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I131" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N131" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O131" s="1" t="n">
+        <v>2029</v>
+      </c>
+      <c r="P131" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q131" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="I131" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K131" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L131" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N131" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O131" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="P131" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="Q131" s="1" t="s">
-        <v>741</v>
-      </c>
       <c r="R131" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T131" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U131" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V131" s="1" t="s">
         <v>38</v>
@@ -11732,25 +11671,25 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B132" s="1" t="s">
+      <c r="E132" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="C132" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>745</v>
-      </c>
       <c r="F132" s="1" t="n">
-        <v>919353250245</v>
+        <v>919035130105</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>28</v>
@@ -11774,10 +11713,10 @@
         <v>2027</v>
       </c>
       <c r="P132" s="1" t="s">
-        <v>746</v>
+        <v>499</v>
       </c>
       <c r="Q132" s="1" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="R132" s="1" t="s">
         <v>35</v>
@@ -11794,28 +11733,28 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="E133" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="F133" s="1" t="n">
-        <v>919611842780</v>
+        <v>917411375549</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>661</v>
+        <v>426</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>29</v>
@@ -11833,22 +11772,19 @@
         <v>4</v>
       </c>
       <c r="O133" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P133" s="1" t="s">
-        <v>190</v>
+        <v>749</v>
       </c>
       <c r="Q133" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="R133" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T133" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U133" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V133" s="1" t="s">
         <v>38</v>
@@ -11856,58 +11792,64 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="B134" s="1" t="s">
+      <c r="E134" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D134" s="1" t="s">
+      <c r="F134" s="1" t="n">
+        <v>918310829211</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="M134" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="N134" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O134" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P134" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="E134" s="1" t="s">
+      <c r="Q134" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="F134" s="1" t="n">
-        <v>919686074527</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L134" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N134" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O134" s="1" t="n">
-        <v>2029</v>
-      </c>
-      <c r="P134" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q134" s="1" t="s">
-        <v>757</v>
-      </c>
       <c r="R134" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T134" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U134" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V134" s="1" t="s">
         <v>38</v>
@@ -11915,40 +11857,40 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D135" s="1" t="s">
+      <c r="E135" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="E135" s="1" t="s">
+      <c r="F135" s="1" t="n">
+        <v>917022969943</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L135" s="1" t="s">
         <v>761</v>
-      </c>
-      <c r="F135" s="1" t="n">
-        <v>919035130105</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H135" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I135" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J135" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="N135" s="1" t="n">
         <v>4</v>
@@ -11957,10 +11899,10 @@
         <v>2027</v>
       </c>
       <c r="P135" s="1" t="s">
-        <v>517</v>
+        <v>762</v>
       </c>
       <c r="Q135" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="R135" s="1" t="s">
         <v>35</v>
@@ -11977,28 +11919,28 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="F136" s="1" t="n">
-        <v>917411375549</v>
+        <v>919591027417</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H136" s="1" t="s">
-        <v>444</v>
+        <v>28</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>29</v>
@@ -12010,7 +11952,7 @@
         <v>31</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="N136" s="1" t="n">
         <v>4</v>
@@ -12019,7 +11961,7 @@
         <v>2027</v>
       </c>
       <c r="P136" s="1" t="s">
-        <v>767</v>
+        <v>44</v>
       </c>
       <c r="Q136" s="1" t="s">
         <v>768</v>
@@ -12029,6 +11971,9 @@
       </c>
       <c r="T136" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U136" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V136" s="1" t="s">
         <v>38</v>
@@ -12051,13 +11996,13 @@
         <v>772</v>
       </c>
       <c r="F137" s="1" t="n">
-        <v>918310829211</v>
+        <v>919886883535</v>
       </c>
       <c r="G137" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>29</v>
@@ -12069,16 +12014,13 @@
         <v>31</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="M137" s="1" t="s">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="N137" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O137" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P137" s="1" t="s">
         <v>773</v>
@@ -12116,13 +12058,13 @@
         <v>778</v>
       </c>
       <c r="F138" s="1" t="n">
-        <v>917022969943</v>
+        <v>917204035964</v>
       </c>
       <c r="G138" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H138" s="1" t="s">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>29</v>
@@ -12134,7 +12076,7 @@
         <v>31</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>779</v>
+        <v>51</v>
       </c>
       <c r="N138" s="1" t="n">
         <v>4</v>
@@ -12143,10 +12085,10 @@
         <v>2027</v>
       </c>
       <c r="P138" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="Q138" s="1" t="s">
         <v>780</v>
-      </c>
-      <c r="Q138" s="1" t="s">
-        <v>781</v>
       </c>
       <c r="R138" s="1" t="s">
         <v>35</v>
@@ -12163,25 +12105,25 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="E139" s="1" t="s">
-        <v>785</v>
-      </c>
       <c r="F139" s="1" t="n">
-        <v>919591027417</v>
+        <v>919448868902</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>28</v>
@@ -12196,19 +12138,19 @@
         <v>31</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="N139" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O139" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P139" s="1" t="s">
-        <v>44</v>
+        <v>773</v>
       </c>
       <c r="Q139" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="R139" s="1" t="s">
         <v>35</v>
@@ -12225,28 +12167,28 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D140" s="1" t="s">
+      <c r="E140" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="E140" s="1" t="s">
-        <v>790</v>
-      </c>
       <c r="F140" s="1" t="n">
-        <v>919886883535</v>
+        <v>919108934881</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H140" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>29</v>
@@ -12258,19 +12200,19 @@
         <v>31</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N140" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O140" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P140" s="1" t="s">
-        <v>791</v>
+        <v>190</v>
       </c>
       <c r="Q140" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="R140" s="1" t="s">
         <v>35</v>
@@ -12287,28 +12229,28 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>796</v>
-      </c>
       <c r="F141" s="1" t="n">
-        <v>917204035964</v>
+        <v>917795002738</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H141" s="1" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>29</v>
@@ -12320,7 +12262,7 @@
         <v>31</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N141" s="1" t="n">
         <v>4</v>
@@ -12329,10 +12271,10 @@
         <v>2027</v>
       </c>
       <c r="P141" s="1" t="s">
-        <v>797</v>
+        <v>190</v>
       </c>
       <c r="Q141" s="1" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="R141" s="1" t="s">
         <v>35</v>
@@ -12349,25 +12291,25 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="E142" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B142" s="1" t="s">
-        <v>800</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>801</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>802</v>
-      </c>
       <c r="F142" s="1" t="n">
-        <v>919448868902</v>
+        <v>919380971427</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H142" s="1" t="s">
         <v>28</v>
@@ -12391,10 +12333,10 @@
         <v>2028</v>
       </c>
       <c r="P142" s="1" t="s">
-        <v>791</v>
+        <v>44</v>
       </c>
       <c r="Q142" s="1" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="R142" s="1" t="s">
         <v>35</v>
@@ -12411,28 +12353,28 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>805</v>
+        <v>226</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="F143" s="1" t="n">
-        <v>919108934881</v>
+        <v>917815941715</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>69</v>
+        <v>426</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>29</v>
@@ -12444,7 +12386,7 @@
         <v>31</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N143" s="1" t="n">
         <v>4</v>
@@ -12453,10 +12395,10 @@
         <v>2027</v>
       </c>
       <c r="P143" s="1" t="s">
-        <v>190</v>
+        <v>749</v>
       </c>
       <c r="Q143" s="1" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="R143" s="1" t="s">
         <v>35</v>
@@ -12473,28 +12415,28 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="1" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="F144" s="1" t="n">
-        <v>917795002738</v>
+        <v>917676325701</v>
       </c>
       <c r="G144" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>28</v>
+        <v>426</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>29</v>
@@ -12506,7 +12448,7 @@
         <v>31</v>
       </c>
       <c r="L144" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N144" s="1" t="n">
         <v>4</v>
@@ -12515,10 +12457,10 @@
         <v>2027</v>
       </c>
       <c r="P144" s="1" t="s">
-        <v>190</v>
+        <v>749</v>
       </c>
       <c r="Q144" s="1" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="R144" s="1" t="s">
         <v>35</v>
@@ -12535,28 +12477,28 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="1" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="F145" s="1" t="n">
-        <v>919380971427</v>
+        <v>919606166109</v>
       </c>
       <c r="G145" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>29</v>
@@ -12568,19 +12510,22 @@
         <v>31</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>51</v>
+        <v>308</v>
+      </c>
+      <c r="M145" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="N145" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O145" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P145" s="1" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="Q145" s="1" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="R145" s="1" t="s">
         <v>35</v>
@@ -12597,28 +12542,28 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>226</v>
+        <v>816</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="F146" s="1" t="n">
-        <v>917815941715</v>
+        <v>917338514557</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>444</v>
+        <v>69</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>29</v>
@@ -12639,10 +12584,10 @@
         <v>2027</v>
       </c>
       <c r="P146" s="1" t="s">
-        <v>767</v>
+        <v>467</v>
       </c>
       <c r="Q146" s="1" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="R146" s="1" t="s">
         <v>35</v>
@@ -12659,28 +12604,28 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="E147" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="B147" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="C147" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>826</v>
-      </c>
       <c r="F147" s="1" t="n">
-        <v>917676325701</v>
+        <v>918792245843</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H147" s="1" t="s">
-        <v>444</v>
+        <v>134</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>29</v>
@@ -12698,13 +12643,13 @@
         <v>4</v>
       </c>
       <c r="O147" s="1" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P147" s="1" t="s">
-        <v>767</v>
+        <v>63</v>
       </c>
       <c r="Q147" s="1" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="R147" s="1" t="s">
         <v>35</v>
@@ -12721,28 +12666,28 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="E148" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>829</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>830</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>831</v>
-      </c>
       <c r="F148" s="1" t="n">
-        <v>919606166109</v>
+        <v>918431907229</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>29</v>
@@ -12754,10 +12699,7 @@
         <v>31</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="M148" s="1" t="s">
-        <v>102</v>
+        <v>308</v>
       </c>
       <c r="N148" s="1" t="n">
         <v>4</v>
@@ -12766,19 +12708,16 @@
         <v>2027</v>
       </c>
       <c r="P148" s="1" t="s">
-        <v>190</v>
+        <v>388</v>
       </c>
       <c r="Q148" s="1" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="R148" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T148" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U148" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V148" s="1" t="s">
         <v>38</v>
@@ -12786,28 +12725,28 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="s">
+        <v>830</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="E149" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="B149" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="C149" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>836</v>
-      </c>
       <c r="F149" s="1" t="n">
-        <v>917338514557</v>
+        <v>917975169785</v>
       </c>
       <c r="G149" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H149" s="1" t="s">
-        <v>69</v>
+        <v>586</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>29</v>
@@ -12819,19 +12758,19 @@
         <v>31</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>51</v>
+        <v>834</v>
       </c>
       <c r="N149" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O149" s="1" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P149" s="1" t="s">
-        <v>485</v>
+        <v>388</v>
       </c>
       <c r="Q149" s="1" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="R149" s="1" t="s">
         <v>35</v>
@@ -12848,52 +12787,52 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="B150" s="1" t="s">
+      <c r="E150" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="C150" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D150" s="1" t="s">
+      <c r="F150" s="1" t="n">
+        <v>919901787236</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N150" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O150" s="1" t="n">
+        <v>2028</v>
+      </c>
+      <c r="P150" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="E150" s="1" t="s">
+      <c r="Q150" s="1" t="s">
         <v>841</v>
-      </c>
-      <c r="F150" s="1" t="n">
-        <v>918792245843</v>
-      </c>
-      <c r="G150" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H150" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I150" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J150" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K150" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L150" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N150" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O150" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="P150" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q150" s="1" t="s">
-        <v>842</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>35</v>
@@ -12910,28 +12849,28 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D151" s="1" t="s">
+      <c r="E151" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>846</v>
-      </c>
       <c r="F151" s="1" t="n">
-        <v>918431907229</v>
+        <v>918431271675</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H151" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>29</v>
@@ -12943,7 +12882,7 @@
         <v>31</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>320</v>
+        <v>51</v>
       </c>
       <c r="N151" s="1" t="n">
         <v>4</v>
@@ -12952,16 +12891,19 @@
         <v>2027</v>
       </c>
       <c r="P151" s="1" t="s">
-        <v>406</v>
+        <v>190</v>
       </c>
       <c r="Q151" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="R151" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T151" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U151" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V151" s="1" t="s">
         <v>38</v>
@@ -12969,52 +12911,52 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="E152" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D152" s="1" t="s">
+      <c r="F152" s="1" t="n">
+        <v>917619533711</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N152" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O152" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P152" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="E152" s="1" t="s">
+      <c r="Q152" s="1" t="s">
         <v>851</v>
-      </c>
-      <c r="F152" s="1" t="n">
-        <v>917975169785</v>
-      </c>
-      <c r="G152" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H152" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="I152" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J152" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K152" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L152" s="1" t="s">
-        <v>852</v>
-      </c>
-      <c r="N152" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O152" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="P152" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="Q152" s="1" t="s">
-        <v>853</v>
       </c>
       <c r="R152" s="1" t="s">
         <v>35</v>
@@ -13031,52 +12973,52 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="B153" s="1" t="s">
+      <c r="E153" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D153" s="1" t="s">
+      <c r="F153" s="1" t="n">
+        <v>917975694842</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N153" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O153" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P153" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="Q153" s="1" t="s">
         <v>856</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="F153" s="1" t="n">
-        <v>919901787236</v>
-      </c>
-      <c r="G153" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H153" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I153" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J153" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K153" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L153" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N153" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O153" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="P153" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="Q153" s="1" t="s">
-        <v>859</v>
       </c>
       <c r="R153" s="1" t="s">
         <v>35</v>
@@ -13093,28 +13035,28 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="E154" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="B154" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>863</v>
-      </c>
       <c r="F154" s="1" t="n">
-        <v>918431271675</v>
+        <v>918073604505</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H154" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>29</v>
@@ -13132,13 +13074,13 @@
         <v>4</v>
       </c>
       <c r="O154" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P154" s="1" t="s">
-        <v>190</v>
+        <v>44</v>
       </c>
       <c r="Q154" s="1" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="R154" s="1" t="s">
         <v>35</v>
@@ -13155,25 +13097,25 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="E155" s="1" t="s">
         <v>865</v>
       </c>
-      <c r="B155" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>867</v>
-      </c>
       <c r="F155" s="1" t="n">
-        <v>917619533711</v>
+        <v>917975821522</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H155" s="1" t="s">
         <v>28</v>
@@ -13194,13 +13136,13 @@
         <v>4</v>
       </c>
       <c r="O155" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P155" s="1" t="s">
-        <v>868</v>
+        <v>44</v>
       </c>
       <c r="Q155" s="1" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="R155" s="1" t="s">
         <v>35</v>
@@ -13217,28 +13159,28 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>871</v>
+        <v>182</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="F156" s="1" t="n">
-        <v>917975694842</v>
+        <v>919741216742</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H156" s="1" t="s">
-        <v>604</v>
+        <v>69</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>29</v>
@@ -13250,7 +13192,7 @@
         <v>31</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="N156" s="1" t="n">
         <v>4</v>
@@ -13259,10 +13201,10 @@
         <v>2027</v>
       </c>
       <c r="P156" s="1" t="s">
-        <v>605</v>
+        <v>190</v>
       </c>
       <c r="Q156" s="1" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="R156" s="1" t="s">
         <v>35</v>
@@ -13279,28 +13221,28 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>918073604505</v>
+        <v>919538123056</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>29</v>
@@ -13318,13 +13260,13 @@
         <v>4</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="P157" s="1" t="s">
-        <v>44</v>
+        <v>875</v>
       </c>
       <c r="Q157" s="1" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>35</v>
@@ -13341,28 +13283,28 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E158" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>883</v>
-      </c>
       <c r="F158" s="1" t="n">
-        <v>917975821522</v>
+        <v>919108413534</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>29</v>
@@ -13374,7 +13316,10 @@
         <v>31</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>51</v>
+        <v>32</v>
+      </c>
+      <c r="M158" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="N158" s="1" t="n">
         <v>4</v>
@@ -13383,10 +13328,10 @@
         <v>2028</v>
       </c>
       <c r="P158" s="1" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="Q158" s="1" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="R158" s="1" t="s">
         <v>35</v>
@@ -13403,28 +13348,28 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>887</v>
-      </c>
       <c r="F159" s="1" t="n">
-        <v>919741216742</v>
+        <v>919481249803</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>29</v>
@@ -13442,13 +13387,13 @@
         <v>4</v>
       </c>
       <c r="O159" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P159" s="1" t="s">
         <v>190</v>
       </c>
       <c r="Q159" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="R159" s="1" t="s">
         <v>35</v>
@@ -13465,29 +13410,29 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="E160" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="C160" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D160" s="1" t="s">
+      <c r="F160" s="1" t="n">
+        <v>919591806236</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H160" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="F160" s="1" t="n">
-        <v>919538123056</v>
-      </c>
-      <c r="G160" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H160" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="I160" s="1" t="s">
         <v>29</v>
       </c>
@@ -13498,7 +13443,7 @@
         <v>31</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>51</v>
+        <v>319</v>
       </c>
       <c r="N160" s="1" t="n">
         <v>4</v>
@@ -13507,10 +13452,10 @@
         <v>2026</v>
       </c>
       <c r="P160" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="Q160" s="1" t="s">
         <v>893</v>
-      </c>
-      <c r="Q160" s="1" t="s">
-        <v>894</v>
       </c>
       <c r="R160" s="1" t="s">
         <v>35</v>
@@ -13527,28 +13472,28 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="B161" s="1" t="s">
+      <c r="C161" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="C161" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D161" s="1" t="s">
+      <c r="E161" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="E161" s="1" t="s">
-        <v>898</v>
-      </c>
       <c r="F161" s="1" t="n">
-        <v>919108413534</v>
+        <v>917795357960</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H161" s="1" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>29</v>
@@ -13562,9 +13507,6 @@
       <c r="L161" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M161" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="N161" s="1" t="n">
         <v>4</v>
       </c>
@@ -13572,7 +13514,7 @@
         <v>2028</v>
       </c>
       <c r="P161" s="1" t="s">
-        <v>190</v>
+        <v>898</v>
       </c>
       <c r="Q161" s="1" t="s">
         <v>899</v>
@@ -13607,7 +13549,7 @@
         <v>903</v>
       </c>
       <c r="F162" s="1" t="n">
-        <v>919481249803</v>
+        <v>919380423971</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>148</v>
@@ -13625,16 +13567,16 @@
         <v>31</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N162" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O162" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P162" s="1" t="s">
-        <v>190</v>
+        <v>474</v>
       </c>
       <c r="Q162" s="1" t="s">
         <v>904</v>
@@ -13669,37 +13611,37 @@
         <v>908</v>
       </c>
       <c r="F163" s="1" t="n">
-        <v>919591806236</v>
+        <v>919113522472</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H163" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I163" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J163" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K163" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N163" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O163" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P163" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q163" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="I163" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J163" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K163" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L163" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="N163" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O163" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="P163" s="1" t="s">
-        <v>910</v>
-      </c>
-      <c r="Q163" s="1" t="s">
-        <v>911</v>
       </c>
       <c r="R163" s="1" t="s">
         <v>35</v>
@@ -13716,52 +13658,52 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="B164" s="1" t="s">
+      <c r="E164" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="C164" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D164" s="1" t="s">
+      <c r="F164" s="1" t="n">
+        <v>918861671363</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I164" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J164" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K164" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L164" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="N164" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O164" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P164" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q164" s="1" t="s">
         <v>914</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="F164" s="1" t="n">
-        <v>917795357960</v>
-      </c>
-      <c r="G164" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H164" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I164" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J164" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K164" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L164" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N164" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O164" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="P164" s="1" t="s">
-        <v>916</v>
-      </c>
-      <c r="Q164" s="1" t="s">
-        <v>917</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>35</v>
@@ -13778,25 +13720,25 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="E165" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>920</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>921</v>
-      </c>
       <c r="F165" s="1" t="n">
-        <v>919380423971</v>
+        <v>917676377870</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H165" s="1" t="s">
         <v>28</v>
@@ -13820,10 +13762,10 @@
         <v>2027</v>
       </c>
       <c r="P165" s="1" t="s">
-        <v>492</v>
+        <v>919</v>
       </c>
       <c r="Q165" s="1" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="R165" s="1" t="s">
         <v>35</v>
@@ -13840,28 +13782,28 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="B166" s="1" t="s">
+      <c r="E166" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="C166" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>926</v>
-      </c>
       <c r="F166" s="1" t="n">
-        <v>919113522472</v>
+        <v>919110431968</v>
       </c>
       <c r="G166" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>28</v>
+        <v>925</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>29</v>
@@ -13873,7 +13815,7 @@
         <v>31</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>51</v>
+        <v>234</v>
       </c>
       <c r="N166" s="1" t="n">
         <v>4</v>
@@ -13882,10 +13824,10 @@
         <v>2027</v>
       </c>
       <c r="P166" s="1" t="s">
-        <v>190</v>
+        <v>467</v>
       </c>
       <c r="Q166" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>35</v>
@@ -13902,28 +13844,28 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D167" s="1" t="s">
+      <c r="E167" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="E167" s="1" t="s">
-        <v>931</v>
-      </c>
       <c r="F167" s="1" t="n">
-        <v>918861671363</v>
+        <v>919148665190</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>29</v>
@@ -13935,7 +13877,7 @@
         <v>31</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>51</v>
+        <v>319</v>
       </c>
       <c r="N167" s="1" t="n">
         <v>4</v>
@@ -13944,10 +13886,10 @@
         <v>2027</v>
       </c>
       <c r="P167" s="1" t="s">
-        <v>190</v>
+        <v>655</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="R167" s="1" t="s">
         <v>35</v>
@@ -13964,22 +13906,22 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B168" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="B168" s="1" t="s">
+      <c r="C168" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="C168" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D168" s="1" t="s">
+      <c r="E168" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="E168" s="1" t="s">
-        <v>936</v>
-      </c>
       <c r="F168" s="1" t="n">
-        <v>917676377870</v>
+        <v>918792690264</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>27</v>
@@ -14006,10 +13948,10 @@
         <v>2027</v>
       </c>
       <c r="P168" s="1" t="s">
-        <v>937</v>
+        <v>427</v>
       </c>
       <c r="Q168" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>35</v>
@@ -14026,28 +13968,28 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="B169" s="1" t="s">
+      <c r="E169" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="C169" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>941</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>942</v>
-      </c>
       <c r="F169" s="1" t="n">
-        <v>919110431968</v>
+        <v>918431508832</v>
       </c>
       <c r="G169" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H169" s="1" t="s">
-        <v>943</v>
+        <v>222</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>29</v>
@@ -14059,7 +14001,7 @@
         <v>31</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>234</v>
+        <v>51</v>
       </c>
       <c r="N169" s="1" t="n">
         <v>4</v>
@@ -14068,10 +14010,10 @@
         <v>2027</v>
       </c>
       <c r="P169" s="1" t="s">
-        <v>485</v>
+        <v>467</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="R169" s="1" t="s">
         <v>35</v>
@@ -14088,28 +14030,28 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="E170" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="B170" s="1" t="s">
-        <v>946</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>948</v>
-      </c>
       <c r="F170" s="1" t="n">
-        <v>919148665190</v>
+        <v>917349156919</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>50</v>
+        <v>222</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>29</v>
@@ -14121,7 +14063,7 @@
         <v>31</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>331</v>
+        <v>51</v>
       </c>
       <c r="N170" s="1" t="n">
         <v>4</v>
@@ -14130,10 +14072,10 @@
         <v>2027</v>
       </c>
       <c r="P170" s="1" t="s">
-        <v>673</v>
+        <v>946</v>
       </c>
       <c r="Q170" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="R170" s="1" t="s">
         <v>35</v>
@@ -14150,22 +14092,22 @@
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="B171" s="1" t="s">
+      <c r="E171" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="C171" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>952</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>953</v>
-      </c>
       <c r="F171" s="1" t="n">
-        <v>918792690264</v>
+        <v>917892363276</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>27</v>
@@ -14192,10 +14134,10 @@
         <v>2027</v>
       </c>
       <c r="P171" s="1" t="s">
-        <v>445</v>
+        <v>190</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>35</v>
@@ -14212,28 +14154,28 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="B172" s="1" t="s">
+      <c r="E172" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="C172" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D172" s="1" t="s">
-        <v>957</v>
-      </c>
-      <c r="E172" s="1" t="s">
-        <v>958</v>
-      </c>
       <c r="F172" s="1" t="n">
-        <v>918431508832</v>
+        <v>917090342305</v>
       </c>
       <c r="G172" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>29</v>
@@ -14245,19 +14187,19 @@
         <v>31</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>51</v>
+        <v>319</v>
       </c>
       <c r="N172" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O172" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P172" s="1" t="s">
-        <v>485</v>
+        <v>63</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>35</v>
@@ -14274,28 +14216,28 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="E173" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>962</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>963</v>
-      </c>
       <c r="F173" s="1" t="n">
-        <v>917349156919</v>
+        <v>917892965871</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>29</v>
@@ -14313,13 +14255,13 @@
         <v>4</v>
       </c>
       <c r="O173" s="1" t="n">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="P173" s="1" t="s">
-        <v>964</v>
+        <v>44</v>
       </c>
       <c r="Q173" s="1" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>35</v>
@@ -14336,25 +14278,25 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>967</v>
+        <v>247</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="F174" s="1" t="n">
-        <v>917892363276</v>
+        <v>917259685448</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H174" s="1" t="s">
         <v>28</v>
@@ -14375,13 +14317,13 @@
         <v>4</v>
       </c>
       <c r="O174" s="1" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="P174" s="1" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>35</v>
@@ -14398,25 +14340,25 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="F175" s="1" t="n">
-        <v>917090342305</v>
+        <v>917019231891</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H175" s="1" t="s">
         <v>28</v>
@@ -14431,7 +14373,7 @@
         <v>31</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>331</v>
+        <v>32</v>
       </c>
       <c r="N175" s="1" t="n">
         <v>4</v>
@@ -14440,10 +14382,10 @@
         <v>2028</v>
       </c>
       <c r="P175" s="1" t="s">
-        <v>63</v>
+        <v>499</v>
       </c>
       <c r="Q175" s="1" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>35</v>
@@ -14460,28 +14402,28 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="F176" s="1" t="n">
-        <v>917892965871</v>
+        <v>919483490977</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>29</v>
@@ -14499,13 +14441,13 @@
         <v>4</v>
       </c>
       <c r="O176" s="1" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="P176" s="1" t="s">
-        <v>44</v>
+        <v>190</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>35</v>
@@ -14522,22 +14464,22 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>253</v>
+        <v>978</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>982</v>
+        <v>979</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>983</v>
+        <v>980</v>
       </c>
       <c r="F177" s="1" t="n">
-        <v>917259685448</v>
+        <v>919740491089</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>148</v>
@@ -14561,22 +14503,19 @@
         <v>4</v>
       </c>
       <c r="O177" s="1" t="n">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="P177" s="1" t="s">
-        <v>63</v>
+        <v>427</v>
       </c>
       <c r="Q177" s="1" t="s">
-        <v>984</v>
+        <v>981</v>
       </c>
       <c r="R177" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T177" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U177" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V177" s="1" t="s">
         <v>38</v>
@@ -14584,22 +14523,22 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="E178" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="B178" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>988</v>
-      </c>
       <c r="F178" s="1" t="n">
-        <v>917019231891</v>
+        <v>919353017591</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>148</v>
@@ -14626,10 +14565,10 @@
         <v>2028</v>
       </c>
       <c r="P178" s="1" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="Q178" s="1" t="s">
-        <v>989</v>
+        <v>986</v>
       </c>
       <c r="R178" s="1" t="s">
         <v>35</v>
@@ -14646,28 +14585,28 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="E179" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>993</v>
-      </c>
       <c r="F179" s="1" t="n">
-        <v>919483490977</v>
+        <v>918971685755</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>29</v>
@@ -14691,7 +14630,7 @@
         <v>190</v>
       </c>
       <c r="Q179" s="1" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>35</v>
@@ -14708,52 +14647,52 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="F180" s="1" t="n">
+        <v>918217200691</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I180" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J180" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K180" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L180" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N180" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O180" s="1" t="n">
+        <v>2027</v>
+      </c>
+      <c r="P180" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q180" s="1" t="s">
         <v>996</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="E180" s="1" t="s">
-        <v>998</v>
-      </c>
-      <c r="F180" s="1" t="n">
-        <v>919740491089</v>
-      </c>
-      <c r="G180" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H180" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I180" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J180" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K180" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L180" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N180" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O180" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="P180" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q180" s="1" t="s">
-        <v>999</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>35</v>
@@ -14767,25 +14706,25 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="B181" s="1" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C181" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D181" s="1" t="s">
-        <v>1002</v>
-      </c>
-      <c r="E181" s="1" t="s">
-        <v>1003</v>
-      </c>
       <c r="F181" s="1" t="n">
-        <v>919353017591</v>
+        <v>917337843016</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H181" s="1" t="s">
         <v>28</v>
@@ -14800,19 +14739,19 @@
         <v>31</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="N181" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O181" s="1" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="P181" s="1" t="s">
-        <v>517</v>
+        <v>63</v>
       </c>
       <c r="Q181" s="1" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="R181" s="1" t="s">
         <v>35</v>
@@ -14829,28 +14768,28 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="B182" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C182" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>1008</v>
-      </c>
       <c r="F182" s="1" t="n">
-        <v>918971685755</v>
+        <v>918546811988</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H182" s="1" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>29</v>
@@ -14868,13 +14807,13 @@
         <v>4</v>
       </c>
       <c r="O182" s="1" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P182" s="1" t="s">
-        <v>190</v>
+        <v>52</v>
       </c>
       <c r="Q182" s="1" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>35</v>
@@ -14891,22 +14830,22 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>1013</v>
-      </c>
       <c r="F183" s="1" t="n">
-        <v>918217200691</v>
+        <v>917892336027</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>27</v>
@@ -14924,7 +14863,7 @@
         <v>31</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>32</v>
+        <v>308</v>
       </c>
       <c r="N183" s="1" t="n">
         <v>4</v>
@@ -14933,16 +14872,19 @@
         <v>2027</v>
       </c>
       <c r="P183" s="1" t="s">
-        <v>190</v>
+        <v>467</v>
       </c>
       <c r="Q183" s="1" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="R183" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T183" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U183" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V183" s="1" t="s">
         <v>38</v>
@@ -14950,25 +14892,25 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>1017</v>
+        <v>152</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="F184" s="1" t="n">
-        <v>917337843016</v>
+        <v>918073972157</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H184" s="1" t="s">
         <v>28</v>
@@ -14983,19 +14925,19 @@
         <v>31</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>43</v>
+        <v>319</v>
       </c>
       <c r="N184" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O184" s="1" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="P184" s="1" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="Q184" s="1" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>35</v>
@@ -15012,28 +14954,28 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="F185" s="1" t="n">
-        <v>918546811988</v>
+        <v>919148832937</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>50</v>
+        <v>492</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>29</v>
@@ -15054,10 +14996,10 @@
         <v>2026</v>
       </c>
       <c r="P185" s="1" t="s">
-        <v>52</v>
+        <v>1020</v>
       </c>
       <c r="Q185" s="1" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="R185" s="1" t="s">
         <v>35</v>
@@ -15074,28 +15016,28 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>1028</v>
-      </c>
       <c r="F186" s="1" t="n">
-        <v>917892336027</v>
+        <v>917975682062</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>27</v>
       </c>
       <c r="H186" s="1" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>29</v>
@@ -15107,28 +15049,25 @@
         <v>31</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>320</v>
+        <v>32</v>
       </c>
       <c r="N186" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O186" s="1" t="n">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="P186" s="1" t="s">
-        <v>485</v>
+        <v>44</v>
       </c>
       <c r="Q186" s="1" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T186" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U186" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V186" s="1" t="s">
         <v>38</v>
@@ -15136,22 +15075,22 @@
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>1032</v>
-      </c>
       <c r="F187" s="1" t="n">
-        <v>918073972157</v>
+        <v>917760704290</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>148</v>
@@ -15169,19 +15108,19 @@
         <v>31</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>331</v>
+        <v>51</v>
       </c>
       <c r="N187" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O187" s="1" t="n">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="P187" s="1" t="s">
         <v>44</v>
       </c>
       <c r="Q187" s="1" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="R187" s="1" t="s">
         <v>35</v>
@@ -15198,28 +15137,28 @@
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="E188" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>1037</v>
-      </c>
       <c r="F188" s="1" t="n">
-        <v>919148832937</v>
+        <v>918792293108</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>148</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>510</v>
+        <v>28</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>29</v>
@@ -15237,13 +15176,13 @@
         <v>4</v>
       </c>
       <c r="O188" s="1" t="n">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="P188" s="1" t="s">
-        <v>1038</v>
+        <v>44</v>
       </c>
       <c r="Q188" s="1" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="R188" s="1" t="s">
         <v>35</v>
@@ -15260,25 +15199,25 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>1040</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>1043</v>
-      </c>
       <c r="F189" s="1" t="n">
-        <v>917975682062</v>
+        <v>918792016026</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>28</v>
@@ -15293,25 +15232,28 @@
         <v>31</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="N189" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O189" s="1" t="n">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="P189" s="1" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="Q189" s="1" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T189" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="U189" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V189" s="1" t="s">
         <v>38</v>
@@ -15319,61 +15261,58 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="B190" s="1" t="s">
+      <c r="F190" s="1" t="n">
+        <v>918431609172</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I190" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J190" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K190" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="L190" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N190" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O190" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="P190" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D190" s="1" t="s">
+      <c r="Q190" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="E190" s="1" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F190" s="1" t="n">
-        <v>917760704290</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H190" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I190" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J190" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K190" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L190" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N190" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O190" s="1" t="n">
-        <v>2029</v>
-      </c>
-      <c r="P190" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q190" s="1" t="s">
-        <v>1049</v>
-      </c>
       <c r="R190" s="1" t="s">
         <v>35</v>
       </c>
       <c r="T190" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="U190" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="V190" s="1" t="s">
         <v>38</v>
@@ -15381,152 +15320,116 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C191" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="E191" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D191" s="1" t="s">
+      <c r="F191" s="1" t="n">
+        <v>918660136124</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I191" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J191" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K191" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="P191" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="E191" s="1" t="s">
+      <c r="T191" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V191" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="F191" s="1" t="n">
-        <v>918792293108</v>
-      </c>
-      <c r="G191" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H191" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I191" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J191" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K191" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L191" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N191" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O191" s="1" t="n">
-        <v>2029</v>
-      </c>
-      <c r="P191" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q191" s="1" t="s">
+      <c r="B192" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="R191" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T191" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U191" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V191" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1" t="s">
+      <c r="C192" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="E192" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="C192" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>1058</v>
-      </c>
       <c r="F192" s="1" t="n">
-        <v>918792016026</v>
-      </c>
-      <c r="G192" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="H192" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I192" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J192" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K192" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="L192" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N192" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O192" s="1" t="n">
-        <v>2028</v>
-      </c>
-      <c r="P192" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q192" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="R192" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T192" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="U192" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V192" s="1" t="s">
+        <v>918660749860</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J192" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K192" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P192" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="T192" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V192" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E193" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="B193" s="1" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>1063</v>
-      </c>
       <c r="F193" s="1" t="n">
-        <v>918431609172</v>
+        <v>918088282948</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>27</v>
+        <v>148</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>134</v>
+        <v>28</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>29</v>
@@ -15537,67 +15440,43 @@
       <c r="K193" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L193" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="N193" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="O193" s="1" t="n">
-        <v>2026</v>
-      </c>
-      <c r="P193" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="Q193" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="R193" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="T193" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V193" s="1" t="s">
+      <c r="P193" s="3" t="s">
+        <v>773</v>
+      </c>
+      <c r="T193" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V193" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="1" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="F194" s="1" t="n">
-        <v>918660136124</v>
+        <v>918050801998</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>148</v>
+        <v>27</v>
       </c>
       <c r="H194" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I194" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J194" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K194" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="P194" s="1" t="s">
-        <v>1070</v>
+        <v>627</v>
       </c>
       <c r="T194" s="3" t="s">
         <v>36</v>
@@ -15607,165 +15486,45 @@
       </c>
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A195" s="0" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B195" s="0" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C195" s="0" t="s">
+      <c r="A195" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C195" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F195" s="0" t="n">
-        <v>918660749860</v>
-      </c>
-      <c r="G195" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H195" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="I195" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="J195" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="K195" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P195" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="T195" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V195" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="0" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B196" s="0" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C196" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="D196" s="0" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E196" s="0" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F196" s="0" t="n">
-        <v>918088282948</v>
-      </c>
-      <c r="G196" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="H196" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="I196" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J196" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K196" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="P196" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="T196" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V196" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A197" s="0" t="s">
-        <v>1079</v>
-      </c>
-      <c r="B197" s="1" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E197" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F197" s="1" t="n">
-        <v>918050801998</v>
-      </c>
-      <c r="G197" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H197" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="P197" s="1" t="s">
-        <v>645</v>
-      </c>
-      <c r="T197" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V197" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="0" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B198" s="1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>1086</v>
-      </c>
-      <c r="F198" s="1" t="n">
+        <v>1068</v>
+      </c>
+      <c r="F195" s="1" t="n">
         <v>917975274584</v>
       </c>
-      <c r="H198" s="4" t="s">
+      <c r="H195" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="P198" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="T198" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V198" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
+      <c r="P195" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="T195" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="V195" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E195" r:id="rId1" display="akshaynagaraj16112005@gmail.com"/>
+    <hyperlink ref="E192" r:id="rId1" display="akshaynagaraj16112005@gmail.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
